--- a/public/layoutadjustmentstok.xlsx
+++ b/public/layoutadjustmentstok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJEK\inventory_bsb\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJEK\PT SYAHID HUSADA DEWATA\inventory_shd\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37A70BE-B17B-4C09-A60F-987FCD867C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A647773-947B-49B4-871D-78C785B50261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>kode</t>
   </si>
@@ -33,19 +33,13 @@
     <t>nama _barang</t>
   </si>
   <si>
-    <t>kode supplier</t>
+    <t>lot</t>
   </si>
   <si>
-    <t>stok total</t>
+    <t>qty</t>
   </si>
   <si>
-    <t>harga beli</t>
-  </si>
-  <si>
-    <t>diskon_persen</t>
-  </si>
-  <si>
-    <t>diskon_rupiah</t>
+    <t>qty total</t>
   </si>
 </sst>
 </file>
@@ -83,7 +77,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -106,14 +100,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -395,41 +406,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>